--- a/data/trans_dic/ProblemasDormirP33b-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 16,56</t>
+          <t>10,75; 16,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,39; 19,48</t>
+          <t>13,29; 19,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 16,82</t>
+          <t>12,56; 16,88</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 13,88</t>
+          <t>8,22; 14,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,77</t>
+          <t>13,91; 20,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 16,26</t>
+          <t>11,81; 15,98</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 16,46</t>
+          <t>3,92; 16,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,64; 32,1</t>
+          <t>21,4; 31,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 19,45</t>
+          <t>5,79; 19,38</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 17,01</t>
+          <t>12,46; 17,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 18,35</t>
+          <t>7,69; 18,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 16,47</t>
+          <t>9,32; 16,39</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,87</t>
+          <t>9,45; 15,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 28,15</t>
+          <t>18,47; 28,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,14; 22,11</t>
+          <t>15,86; 22,03</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 16,52</t>
+          <t>4,19; 15,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,12; 23,88</t>
+          <t>19,17; 24,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,28; 20,78</t>
+          <t>16,21; 20,91</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,55</t>
+          <t>9,65; 13,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,61; 21,02</t>
+          <t>15,51; 20,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,74; 17,15</t>
+          <t>13,8; 17,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52339; 83670</t>
+          <t>54294; 84428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59915; 87181</t>
+          <t>59449; 86603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119481; 160212</t>
+          <t>119671; 160855</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36708; 62781</t>
+          <t>37190; 64422</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54344; 79453</t>
+          <t>53212; 79059</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99146; 135712</t>
+          <t>98558; 133440</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22418; 110008</t>
+          <t>26220; 112405</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36116; 53572</t>
+          <t>35725; 53115</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46901; 162411</t>
+          <t>48360; 161837</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130295; 176041</t>
+          <t>128889; 176854</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65067; 179460</t>
+          <t>75251; 178144</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204343; 331606</t>
+          <t>187563; 330001</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44592; 70639</t>
+          <t>44905; 72282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151303; 236837</t>
+          <t>155411; 239591</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>212454; 291100</t>
+          <t>208810; 289986</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9780; 39731</t>
+          <t>10079; 38090</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145563; 181825</t>
+          <t>145970; 183871</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163057; 208218</t>
+          <t>162416; 209537</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>319437; 457600</t>
+          <t>325627; 461645</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>558339; 752079</t>
+          <t>554819; 751014</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>955790; 1192808</t>
+          <t>959732; 1184102</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProblemasDormirP33b-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 16,71</t>
+          <t>10,68; 16,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 19,35</t>
+          <t>14,03; 20,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 16,88</t>
+          <t>12,98; 17,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 14,25</t>
+          <t>8,48; 14,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 20,66</t>
+          <t>14,73; 21,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 15,98</t>
+          <t>12,07; 16,27</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 16,82</t>
+          <t>12,24; 19,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,4; 31,82</t>
+          <t>21,21; 31,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 19,38</t>
+          <t>15,83; 21,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 17,09</t>
+          <t>12,87; 17,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 18,21</t>
+          <t>15,53; 20,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 16,39</t>
+          <t>14,75; 17,69</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 15,22</t>
+          <t>9,12; 14,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 28,48</t>
+          <t>24,59; 29,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,86; 22,03</t>
+          <t>18,86; 22,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 15,84</t>
+          <t>4,25; 15,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,15</t>
+          <t>18,78; 23,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,21; 20,91</t>
+          <t>16,4; 20,92</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 13,67</t>
+          <t>12,02; 14,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 20,99</t>
+          <t>19,83; 22,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,8; 17,03</t>
+          <t>16,25; 17,98</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66917</t>
+          <t>73185</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>81374</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139376</t>
+          <t>154560</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54294; 84428</t>
+          <t>58803; 91542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59449; 86603</t>
+          <t>68511; 97969</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119671; 160855</t>
+          <t>134833; 178474</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>53146</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115496</t>
+          <t>127325</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37190; 64422</t>
+          <t>40982; 68428</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53212; 79059</t>
+          <t>62318; 90337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98558; 133440</t>
+          <t>109413; 147495</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>72279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44268</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110606</t>
+          <t>122159</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26220; 112405</t>
+          <t>57729; 89941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35725; 53115</t>
+          <t>39760; 59497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48360; 161837</t>
+          <t>104332; 140161</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>151724</t>
+          <t>168533</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>134541</t>
+          <t>152795</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286265</t>
+          <t>321328</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>128889; 176854</t>
+          <t>145621; 195195</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75251; 178144</t>
+          <t>133711; 172610</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>187563; 330001</t>
+          <t>294069; 352600</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56260</t>
+          <t>65106</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>203675</t>
+          <t>224010</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>259935</t>
+          <t>289116</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44905; 72282</t>
+          <t>51788; 81975</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>155411; 239591</t>
+          <t>204307; 244903</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208810; 289986</t>
+          <t>263875; 318721</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>20644</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>164194</t>
+          <t>180640</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184838</t>
+          <t>199387</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10079; 38090</t>
+          <t>10086; 35703</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145970; 183871</t>
+          <t>158553; 199789</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162416; 209537</t>
+          <t>177396; 226250</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>411117</t>
+          <t>450996</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>685397</t>
+          <t>762878</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1096515</t>
+          <t>1213874</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>325627; 461645</t>
+          <t>413837; 496393</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>554819; 751014</t>
+          <t>720895; 804732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>959732; 1184102</t>
+          <t>1150470; 1272761</t>
         </is>
       </c>
     </row>
